--- a/product_upload/packages/44/file.xlsx
+++ b/product_upload/packages/44/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Isolone</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-578752AB31E3</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1042,6 +1052,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Isolone</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-0136B9263758</t>
         </is>
       </c>
@@ -1065,7 +1080,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Lenova</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-309916E6E693</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1418,6 +1438,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Ferasiro 90</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-2ECEFFD009C6</t>
         </is>
       </c>
@@ -1441,7 +1466,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1610,6 +1635,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Ferasiro 180</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-A5562E6AE821</t>
         </is>
       </c>
@@ -1633,7 +1663,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1802,6 +1832,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Ferasiro 360</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-0E92B7C5AC20</t>
         </is>
       </c>
@@ -1825,7 +1860,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1986,6 +2021,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>SENERGY PLUS (10/160/25)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-B48DCE5B3FFA</t>
         </is>
       </c>
@@ -2009,7 +2049,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2174,6 +2214,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>SENERGY PLUS (10/160/12.5)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-3778EA9E66AC</t>
         </is>
       </c>
@@ -2197,7 +2242,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2362,6 +2407,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>SENERGY PLUS (5/160/25)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-0460F5437B32</t>
         </is>
       </c>
@@ -2385,7 +2435,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2550,6 +2600,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>SENERGY PLUS (5/160/12.5)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-AD156C548AF6</t>
         </is>
       </c>
@@ -2573,7 +2628,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2736,6 +2791,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>SCOLTA 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-3D41FE836D14</t>
         </is>
       </c>
@@ -2759,7 +2819,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2922,6 +2982,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>SCOLTA 20MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-6DBF35B2069D</t>
         </is>
       </c>
@@ -2945,7 +3010,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3108,6 +3173,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>SCOLTA 40MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-1E0B67F44A33</t>
         </is>
       </c>
@@ -3131,7 +3201,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3290,6 +3360,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CROTAL 1MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-7EF85D464D24</t>
         </is>
       </c>
@@ -3313,7 +3388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3472,6 +3547,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>CROTAL 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-4D7B06ADDEB0</t>
         </is>
       </c>
@@ -3495,7 +3575,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3666,6 +3746,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t xml:space="preserve">JANUMET XR </t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-24BA2132DCCA</t>
         </is>
       </c>
@@ -3689,7 +3774,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3860,6 +3945,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t xml:space="preserve">JANUMET XR </t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-15A16D3E5769</t>
         </is>
       </c>
@@ -3883,7 +3973,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4058,6 +4148,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t xml:space="preserve">JANUMET XR </t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-D585F02DEF39</t>
         </is>
       </c>
@@ -4081,7 +4176,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4248,6 +4343,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>RIVAXEL 4.6MG/24HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-6AAB86DE6801</t>
         </is>
       </c>
@@ -4271,7 +4371,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4438,6 +4538,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>RIVAXEL 9.5MG/24HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-F34213028C1F</t>
         </is>
       </c>
@@ -4461,7 +4566,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4616,6 +4721,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>RIVAXEL 13.3MG/24HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-F8949C87BF7C</t>
         </is>
       </c>
@@ -4639,7 +4749,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>DECOZAL 0.05% METERED DOSE NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-4DAD4FB64851</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4988,6 +5103,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>MALAUST</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-CAABF832F5FD</t>
         </is>
       </c>
@@ -5011,7 +5131,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5182,6 +5302,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Hyrimoz</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-5C50DC67B870</t>
         </is>
       </c>
@@ -5205,7 +5330,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5368,6 +5493,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Hyrimoz</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-87F534374D41</t>
         </is>
       </c>
@@ -5391,7 +5521,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5554,6 +5684,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Exopex</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-EF8F9A63568E</t>
         </is>
       </c>
@@ -5577,7 +5712,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5736,6 +5871,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Exopex</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-07CE26B77D50</t>
         </is>
       </c>
@@ -5759,7 +5899,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5922,6 +6062,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>RAFLOX</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-FD317C6CBE48</t>
         </is>
       </c>
@@ -5945,7 +6090,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6104,6 +6249,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>RAFLOX</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-2D3160A53756</t>
         </is>
       </c>
@@ -6127,7 +6277,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6302,6 +6452,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>RAFLOX</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-AEB94E791D09</t>
         </is>
       </c>
@@ -6325,7 +6480,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6492,6 +6647,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>L-CET</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-CDCB82BBECE2</t>
         </is>
       </c>
@@ -6515,7 +6675,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6682,6 +6842,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CALMAR</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-2E89A9C8595F</t>
         </is>
       </c>
@@ -6705,7 +6870,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6872,6 +7037,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>OZAPIN</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-3F96130E6F0E</t>
         </is>
       </c>
@@ -6895,7 +7065,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7058,6 +7228,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>OZAPIN</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-2B90ED4BE7ED</t>
         </is>
       </c>
@@ -7081,7 +7256,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7238,6 +7413,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Eligon</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-08728B25CF4A</t>
         </is>
       </c>
@@ -7261,7 +7441,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7434,6 +7614,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Pixar</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-12B6E4CFDCB8</t>
         </is>
       </c>
@@ -7457,7 +7642,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7630,6 +7815,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Pixar</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-A6A2508F2E6B</t>
         </is>
       </c>
@@ -7653,7 +7843,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7824,6 +8014,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Olsar Plus</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-998973BD30D8</t>
         </is>
       </c>
@@ -7847,7 +8042,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8018,6 +8213,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Olsar Plus</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-FABA138130A9</t>
         </is>
       </c>
@@ -8041,7 +8241,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8212,6 +8412,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Olsar Plus</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-5954B93D1C2B</t>
         </is>
       </c>
@@ -8235,7 +8440,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8414,6 +8619,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Triolite</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-F8FAEAED4F08</t>
         </is>
       </c>
@@ -8437,7 +8647,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8600,6 +8810,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-34AFCA88054B</t>
         </is>
       </c>
@@ -8623,7 +8838,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8790,6 +9005,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-7FA1D7A39D01</t>
         </is>
       </c>
@@ -8813,7 +9033,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8972,6 +9192,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-CDB015A01771</t>
         </is>
       </c>
@@ -8995,7 +9220,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9166,6 +9391,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-E21DE76374DD</t>
         </is>
       </c>
@@ -9189,7 +9419,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9364,6 +9594,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-09938C2C1519</t>
         </is>
       </c>
@@ -9387,7 +9622,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9558,6 +9793,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-A2208D4472BB</t>
         </is>
       </c>
@@ -9581,7 +9821,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9756,6 +9996,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Inhixa</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-68500FEE8066</t>
         </is>
       </c>
@@ -9779,7 +10024,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9938,6 +10183,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>DANDAXA</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-79FD41112B8A</t>
         </is>
       </c>
@@ -9961,7 +10211,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10124,6 +10374,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>DANDAXA</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-0303BFA39EBE</t>
         </is>
       </c>
@@ -10147,7 +10402,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10310,6 +10565,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>CO-ZANSOR 150/12.5MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-754DBF69695F</t>
         </is>
       </c>
@@ -10333,7 +10593,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10492,6 +10752,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>CO-ZANSOR 300/12.5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-38105BCC8D16</t>
         </is>
       </c>
@@ -10515,7 +10780,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10670,6 +10935,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>CO-ZANSOR 300/25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-7A36428F9CA0</t>
         </is>
       </c>
@@ -10693,7 +10963,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10860,6 +11130,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>LEZAL</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-3794471D37E2</t>
         </is>
       </c>
@@ -10883,7 +11158,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11046,6 +11321,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>AMLOVAN-HCT 10/160/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-E620EAE14D25</t>
         </is>
       </c>
@@ -11069,7 +11349,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11228,6 +11508,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>AMLOVAN-HCT 10/160/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-8D1E7932F8F5</t>
         </is>
       </c>
@@ -11251,7 +11536,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11410,6 +11695,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>AMLOVAN-HCT 5/160//25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-A5F0751C15CD</t>
         </is>
       </c>
@@ -11433,7 +11723,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11596,6 +11886,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>AMLOVAN-HCT 5/160/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-72BBF1A48B13</t>
         </is>
       </c>
@@ -11619,7 +11914,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11778,6 +12073,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>VILTIN 50 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-8E5C49047105</t>
         </is>
       </c>
@@ -11801,7 +12101,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11968,6 +12268,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>ARIPEX 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-3ACC50E37D6E</t>
         </is>
       </c>
@@ -11991,7 +12296,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12162,6 +12467,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>XIFAXAN 200MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-21F017C0F00C</t>
         </is>
       </c>
@@ -12185,7 +12495,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12348,6 +12658,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>FLAMEX 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-7112177C2F16</t>
         </is>
       </c>
@@ -12371,7 +12686,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12534,6 +12849,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>FLAMEX 200 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-0B5AACE1606A</t>
         </is>
       </c>
@@ -12557,7 +12877,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12732,6 +13052,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Sildenafil OHRE Pharma</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-6777F368D0DC</t>
         </is>
       </c>
@@ -12755,7 +13080,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12922,6 +13247,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>BOSULIF</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-D33703166713</t>
         </is>
       </c>
@@ -12945,7 +13275,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13116,6 +13446,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Otipax</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-00612F7CC5E7</t>
         </is>
       </c>
@@ -13139,7 +13474,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13302,6 +13637,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ATOX</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-477CE06C3917</t>
         </is>
       </c>
@@ -13325,7 +13665,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13484,6 +13824,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>ATOX</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-F1E8D15CB5F2</t>
         </is>
       </c>
@@ -13507,7 +13852,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13666,6 +14011,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>ATOX</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-F347AB7D0A81</t>
         </is>
       </c>
@@ -13689,7 +14039,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13852,6 +14202,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Tedo 5 film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-FC1867F44DA7</t>
         </is>
       </c>
@@ -13875,7 +14230,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14042,6 +14397,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>FOLICRON SR CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-90F3FA95B965</t>
         </is>
       </c>
@@ -14065,7 +14425,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14242,6 +14602,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-2BC70F635355</t>
         </is>
       </c>
@@ -14265,7 +14630,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14434,6 +14799,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-553898550D22</t>
         </is>
       </c>
@@ -14457,7 +14827,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14630,6 +15000,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-7A8853351843</t>
         </is>
       </c>
@@ -14653,7 +15028,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14826,6 +15201,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Durotine</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-097B41C1F067</t>
         </is>
       </c>
@@ -14849,7 +15229,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15018,6 +15398,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Durotine</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-0125E5FA4D6F</t>
         </is>
       </c>
@@ -15041,7 +15426,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15214,6 +15599,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Reagila</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-A3B1F36E3573</t>
         </is>
       </c>
@@ -15237,7 +15627,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15414,6 +15804,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Reagila</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-B95555CE50D8</t>
         </is>
       </c>
@@ -15437,7 +15832,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15610,6 +16005,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>Reagila</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-7384D4197D06</t>
         </is>
       </c>
@@ -15633,7 +16033,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15806,6 +16206,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Reagila</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-FB60DF36B834</t>
         </is>
       </c>
@@ -15829,7 +16234,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16000,6 +16405,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Crotal</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-DFABCC5B8F21</t>
         </is>
       </c>
@@ -16023,7 +16433,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16182,6 +16592,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Lamsev 800</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D48C49FBCDF6</t>
         </is>
       </c>
@@ -16205,7 +16620,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16382,6 +16797,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Tredia</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-7BA533025BFB</t>
         </is>
       </c>
@@ -16405,7 +16825,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16574,6 +16994,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Tredia</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-5A3DA5989BAC</t>
         </is>
       </c>
@@ -16597,7 +17022,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16764,6 +17189,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>NEURITAM</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-A3B9676DBE6E</t>
         </is>
       </c>
@@ -16787,7 +17217,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16950,6 +17380,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>NEURITAM</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-86FF97418BAC</t>
         </is>
       </c>
@@ -16973,7 +17408,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17140,6 +17575,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Ocaliva</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-6C82360A354F</t>
         </is>
       </c>
@@ -17163,7 +17603,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17330,6 +17770,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Ocaliva</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-C42F6E8A0733</t>
         </is>
       </c>
@@ -17353,7 +17798,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17516,6 +17961,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Etimicol 10</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-36CDFDE9DACE</t>
         </is>
       </c>
@@ -17539,7 +17989,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17706,6 +18156,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Trientine dihydrochloride</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-E941F2819BFB</t>
         </is>
       </c>
@@ -17729,7 +18184,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17898,6 +18353,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Tyrox</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-7B21FC285BEE</t>
         </is>
       </c>
@@ -17921,7 +18381,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18098,6 +18558,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Rivaroxaban SPC</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-540289D198E6</t>
         </is>
       </c>
@@ -18121,7 +18586,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18290,6 +18755,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Rivaroxaban SPC</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-8481BDBE8E26</t>
         </is>
       </c>
@@ -18313,7 +18783,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18490,6 +18960,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Rivaroxaban SPC</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-8122E623EBF8</t>
         </is>
       </c>
@@ -18513,7 +18988,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18680,6 +19155,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Montas</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-020C42CECF72</t>
         </is>
       </c>
@@ -18703,7 +19183,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18866,6 +19346,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Bosentan OHRE Pharma</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-B2FD067D7759</t>
         </is>
       </c>
@@ -18889,7 +19374,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19054,6 +19539,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-67BD62D5302D</t>
         </is>
       </c>
@@ -19077,7 +19567,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19240,6 +19730,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-E2AA3676E47B</t>
         </is>
       </c>
@@ -19263,7 +19758,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19440,6 +19935,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-D05603F44220</t>
         </is>
       </c>
@@ -19463,7 +19963,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19627,6 +20127,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-2707B3AE717E</t>
         </is>
@@ -19643,7 +20148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19689,100 +20194,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19814,7 +20324,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19829,92 +20339,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-25523</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>317.61</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>408</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19946,7 +20461,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19961,92 +20476,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-37929</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>23.51</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>409</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20078,7 +20598,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20093,92 +20613,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-84249</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>247.83</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>410</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20210,7 +20735,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20225,92 +20750,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-88828</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>136.55</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>411</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20342,7 +20872,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20357,92 +20887,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-46784</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>268.08</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>412</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20474,7 +21009,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20489,92 +21024,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-94327</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>441.93</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>413</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20606,7 +21146,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20621,92 +21161,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-93961</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>79.62</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>414</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20738,7 +21283,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20753,92 +21298,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-27927</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>351.57</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>415</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20870,7 +21420,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20885,92 +21435,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-83530</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>73.11</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>416</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21002,7 +21557,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21017,92 +21572,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-34576</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>499.78</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>417</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21134,7 +21694,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21149,92 +21709,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-47369</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>266.77</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>418</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21251,7 +21816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21357,6 +21922,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21392,7 +21967,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21457,6 +22032,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-FB3E6592FC55</t>
         </is>
@@ -21493,7 +22078,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21558,6 +22143,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-AF12807580B1</t>
         </is>
@@ -21594,7 +22189,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21659,6 +22254,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-CBFF74D0FFE8</t>
         </is>
@@ -21695,7 +22300,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21760,6 +22365,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-8FD1C7872BAF</t>
         </is>
@@ -21796,7 +22411,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21861,6 +22476,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-7373C0658988</t>
         </is>
@@ -21897,7 +22522,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21962,6 +22587,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-FA1301703E0E</t>
         </is>
@@ -21998,7 +22633,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22063,6 +22698,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-2104E9BEDE42</t>
         </is>
@@ -22099,7 +22744,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22164,6 +22809,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-4FCCC56A3E99</t>
         </is>
@@ -22200,7 +22855,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22265,6 +22920,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-808F3E0A8708</t>
         </is>
@@ -22301,7 +22966,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22366,6 +23031,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-BAA6E2BEDFA2</t>
         </is>
@@ -22402,7 +23077,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22467,6 +23142,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-D07BD9735EE8</t>
         </is>
@@ -22503,7 +23188,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22568,6 +23253,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-9930D8D75A50</t>
         </is>
@@ -22604,7 +23299,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22669,6 +23364,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-FDFE25870A2F</t>
         </is>
@@ -22705,7 +23410,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22770,6 +23475,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-630585B7AA56</t>
         </is>
@@ -22806,7 +23521,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22871,6 +23586,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-4FA28FB903BE</t>
         </is>
@@ -22907,7 +23632,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22972,6 +23697,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-C51C47A7B0E0</t>
         </is>
@@ -23008,7 +23743,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23073,6 +23808,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-377A500D025D</t>
         </is>
@@ -23109,7 +23854,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23174,6 +23919,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-6A1E490BDBBB</t>
         </is>
@@ -23210,7 +23965,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23275,6 +24030,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-2967737033FB</t>
         </is>
@@ -23311,7 +24076,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23376,6 +24141,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-5C34827235C1</t>
         </is>

--- a/product_upload/packages/44/file.xlsx
+++ b/product_upload/packages/44/file.xlsx
@@ -686,8 +686,16 @@
           <t>0398897602-343-109371638100</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Isolone</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Isolone detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1088,8 +1096,16 @@
           <t>4097861459-003-362364327559</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lenova</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lenova detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1868,8 +1884,16 @@
           <t>8490052062-736-563446529742</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SENERGY PLUS (10/160/25)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SENERGY PLUS (10/160/25)MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2057,8 +2081,16 @@
           <t>0264053391-095-897444472504</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SENERGY PLUS (10/160/12.5)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SENERGY PLUS (10/160/12.5)MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2250,8 +2282,16 @@
           <t>0906964412-369-990073669955</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SENERGY PLUS (5/160/25)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SENERGY PLUS (5/160/25)MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2443,8 +2483,16 @@
           <t>1524970468-810-466837694722</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SENERGY PLUS (5/160/12.5)MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SENERGY PLUS (5/160/12.5)MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2636,8 +2684,16 @@
           <t>7170237772-506-334012235173</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCOLTA 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SCOLTA 10MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2827,8 +2883,16 @@
           <t>7150452688-311-913749614594</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCOLTA 20MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SCOLTA 20MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3018,8 +3082,16 @@
           <t>3453232653-769-030856055174</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCOLTA 40MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SCOLTA 40MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3209,8 +3281,16 @@
           <t>7849503140-002-299410128256</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CROTAL 1MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CROTAL 1MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3396,8 +3476,16 @@
           <t>7112577220-181-022429519310</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CROTAL 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CROTAL 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -4574,8 +4662,16 @@
           <t>7734460370-153-155112623543</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIVAXEL 13.3MG/24HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>RIVAXEL 13.3MG/24HRS TRANSDERMAL PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4757,8 +4853,16 @@
           <t>1226631543-826-658255690550</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DECOZAL 0.05% METERED DOSE NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DECOZAL 0.05% METERED DOSE NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5139,8 +5243,16 @@
           <t>8230432824-185-348615945879</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hyrimoz</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hyrimoz detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5338,8 +5450,16 @@
           <t>5678384861-376-376225305154</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hyrimoz</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hyrimoz detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5529,8 +5649,16 @@
           <t>9613962309-822-241982191174</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exopex</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Exopex detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5720,8 +5848,16 @@
           <t>9265805174-573-671403051364</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exopex</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Exopex detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5907,8 +6043,16 @@
           <t>0083189925-998-133195425669</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RAFLOX</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>RAFLOX detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6098,8 +6242,16 @@
           <t>5278359548-899-370300930853</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RAFLOX</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RAFLOX detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6683,8 +6835,16 @@
           <t>5013079552-265-281060673431</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALMAR</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CALMAR detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6878,8 +7038,16 @@
           <t>4478114620-558-329987616154</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OZAPIN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>OZAPIN detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7073,8 +7241,16 @@
           <t>4390593746-195-349649070897</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OZAPIN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>OZAPIN detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7264,8 +7440,16 @@
           <t>2651267070-972-588178876191</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eligon</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Eligon detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Sudair Pharma Company</t>
@@ -8655,8 +8839,16 @@
           <t>8877871242-779-442546194040</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Inhixa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Inhixa detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8846,8 +9038,16 @@
           <t>0980565940-482-410053770815</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Inhixa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Inhixa detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9041,8 +9241,16 @@
           <t>2981709391-522-577944643126</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Inhixa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Inhixa detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -10032,8 +10240,16 @@
           <t>3616164593-052-409715242884</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DANDAXA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DANDAXA detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10219,8 +10435,16 @@
           <t>0211710099-576-561640282705</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DANDAXA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DANDAXA detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10410,8 +10634,16 @@
           <t>5640510800-203-852548243739</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ZANSOR 150/12.5MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CO-ZANSOR 150/12.5MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10601,8 +10833,16 @@
           <t>8499761167-530-494412444150</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ZANSOR 300/12.5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CO-ZANSOR 300/12.5MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10788,8 +11028,16 @@
           <t>8403756485-928-069244112427</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-ZANSOR 300/25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CO-ZANSOR 300/25MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11166,8 +11414,16 @@
           <t>7645673538-490-669498334658</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOVAN-HCT 10/160/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AMLOVAN-HCT 10/160/25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11357,8 +11613,16 @@
           <t>7689389683-796-405429879299</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOVAN-HCT 10/160/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AMLOVAN-HCT 10/160/12.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11544,8 +11808,16 @@
           <t>8223527709-525-304133564234</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOVAN-HCT 5/160//25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>AMLOVAN-HCT 5/160//25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11731,8 +12003,16 @@
           <t>2862095232-443-441357696641</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOVAN-HCT 5/160/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AMLOVAN-HCT 5/160/12.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11922,8 +12202,16 @@
           <t>9755673814-274-328358999285</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VILTIN 50 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>VILTIN 50 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12109,8 +12397,16 @@
           <t>7499584510-661-484224134831</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARIPEX 2MG TABLET</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ARIPEX 2MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12503,8 +12799,16 @@
           <t>8473020930-842-556914849325</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLAMEX 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>FLAMEX 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12694,8 +12998,16 @@
           <t>3747469706-267-929445491454</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLAMEX 200 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>FLAMEX 200 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13088,8 +13400,16 @@
           <t>0933299619-020-747880143536</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BOSULIF</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BOSULIF detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13482,8 +13802,16 @@
           <t>1045311978-618-471692065354</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATOX</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ATOX detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13673,8 +14001,16 @@
           <t>3912623271-847-617802460280</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATOX</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ATOX detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13860,8 +14196,16 @@
           <t>1860703936-436-082908134992</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATOX</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ATOX detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14238,8 +14582,16 @@
           <t>6267612540-634-813957142847</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOLICRON SR CAPSULE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>FOLICRON SR CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -16441,8 +16793,16 @@
           <t>6116102055-251-184293746135</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lamsev 800</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Lamsev 800 detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -17225,8 +17585,16 @@
           <t>9382778051-515-886101155030</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEURITAM</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>NEURITAM detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17416,8 +17784,16 @@
           <t>1551247535-138-741418601310</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ocaliva</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ocaliva detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17611,8 +17987,16 @@
           <t>9175976654-644-581720286129</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ocaliva</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ocaliva detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17806,8 +18190,16 @@
           <t>7255949518-157-204723836844</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etimicol 10</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Etimicol 10 detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17997,8 +18389,16 @@
           <t>7425506711-650-737133277711</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trientine dihydrochloride</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Trientine dihydrochloride detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18192,8 +18592,16 @@
           <t>1230043686-232-566328695794</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tyrox</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Tyrox detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -18996,8 +19404,16 @@
           <t>3664870507-465-707910335671</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Montas</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Montas detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19191,8 +19607,16 @@
           <t>5160631620-542-210690986238</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bosentan OHRE Pharma</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bosentan OHRE Pharma detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19382,8 +19806,16 @@
           <t>0656241204-098-178604558823</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Dimethyl Fumarate SPC detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Sudair Pharma Company</t>
@@ -19575,8 +20007,16 @@
           <t>8832038979-889-793127823464</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Dimethyl Fumarate SPC detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19971,8 +20411,16 @@
           <t>7308946218-605-284141799481</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dimethyl Fumarate SPC</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Dimethyl Fumarate SPC detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>Sudair Pharma Company</t>

--- a/product_upload/packages/44/file.xlsx
+++ b/product_upload/packages/44/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22264,7 +22264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22345,40 +22345,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22458,38 +22463,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>330.7</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-FB3E6592FC55</t>
         </is>
@@ -22569,38 +22579,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>283.05</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-AF12807580B1</t>
         </is>
@@ -22680,38 +22695,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>425.66</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-CBFF74D0FFE8</t>
         </is>
@@ -22791,38 +22811,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>205.81</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-8FD1C7872BAF</t>
         </is>
@@ -22902,38 +22927,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>464.83</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-7373C0658988</t>
         </is>
@@ -23013,38 +23043,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>232.49</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-FA1301703E0E</t>
         </is>
@@ -23124,38 +23159,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>92.51000000000001</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-2104E9BEDE42</t>
         </is>
@@ -23235,38 +23275,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>272.22</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-4FCCC56A3E99</t>
         </is>
@@ -23346,38 +23391,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>476</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-808F3E0A8708</t>
         </is>
@@ -23457,38 +23507,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>359.66</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-BAA6E2BEDFA2</t>
         </is>
@@ -23568,38 +23623,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>169.77</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-D07BD9735EE8</t>
         </is>
@@ -23679,38 +23739,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>304.07</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-9930D8D75A50</t>
         </is>
@@ -23790,38 +23855,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>494.05</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-FDFE25870A2F</t>
         </is>
@@ -23901,38 +23971,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>25.3</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-630585B7AA56</t>
         </is>
@@ -24012,38 +24087,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>356.51</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-4FA28FB903BE</t>
         </is>
@@ -24123,38 +24203,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>298.14</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-C51C47A7B0E0</t>
         </is>
@@ -24234,38 +24319,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>418.7</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-377A500D025D</t>
         </is>
@@ -24345,38 +24435,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>141.52</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-6A1E490BDBBB</t>
         </is>
@@ -24456,38 +24551,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>192.85</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-2967737033FB</t>
         </is>
@@ -24567,38 +24667,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>391.96</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-5C34827235C1</t>
         </is>
